--- a/Aula_14/banco_tabajara.xlsx
+++ b/Aula_14/banco_tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,54 @@
         <v>402</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>paulo</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>456</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>seila</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>403</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pedro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>654</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ainn</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>404</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Aula_14/banco_tabajara.xlsx
+++ b/Aula_14/banco_tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nome_cli</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -482,18 +482,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>321</v>
+        <v>123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>402</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>paulo</t>
+          <t>pedro</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -517,7 +517,7 @@
         <v>403</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -526,21 +526,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pedro</t>
+          <t>jaoo</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>654</v>
+        <v>123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ainn</t>
+          <t>corrente</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>404</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>jaoo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>123</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>poupança</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>405</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
